--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0197.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0197.xlsx
@@ -834,7 +834,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Đúng vậy.</t>
+          <t>Đúng, tôi đây.</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Ôi. Nhưng mà để trở thành Vũ Công Sư Tử đâu phải chuyện đơn giản đâu, cậu biết không?</t>
+          <t>Ôi. Nhưng mà để trở thành Vũ Công Sư Tử đâu phải chuyện đơn giản đâu, bạn biết không?</t>
         </is>
       </c>
     </row>
@@ -4279,7 +4279,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Xin chào, Rover. Ta nghĩ chúng ta đã gặp nhau một lần rồi.</t>
+          <t>Xin chào, Vận Mệnh Giả. Ta nghĩ chúng ta đã gặp nhau một lần rồi.</t>
         </is>
       </c>
     </row>
@@ -5449,7 +5449,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Cậu nghĩ con sư tử sẽ xuất hiện từ bên nào? Trái hay phải?</t>
+          <t>Mày nghĩ con sư tử sẽ xuất hiện từ bên nào? Trái hay phải?</t>
         </is>
       </c>
     </row>
@@ -5644,7 +5644,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Nhưng ta đã nói hết những gì mình biết rồi mà...</t>
+          <t>Nhưng tao đã nói hết những gì mình biết rồi mà...</t>
         </is>
       </c>
     </row>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>Nó... Nó là... một người bạn của ta.</t>
+          <t>Nó... Nó là... một người bạn của tao.</t>
         </is>
       </c>
     </row>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Cậu ổn chứ?</t>
+          <t>Cậu ổn không?</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Ngày 2: Chơi Echo Simulation cả ngày.</t>
+          <t>Ngày 2: Played Echo Simulation all day.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Ngày 3: Chơi Echo Simulation cả ngày.</t>
+          <t>Ngày 3: Played Echo Simulation all day.</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Ngày 5: Chơi Echo Simulation cả ngày.</t>
+          <t>Ngày 5: Played Echo Simulation all day.</t>
         </is>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Chẳng có thú dữ nào cả, chỉ toàn mấy kẻ Lưu Đày phá ngày của ta. Mất thêm mấy kiện hàng nữa. Hỏng cả thiết bị đầu cuối. Giờ chẳng chạy được Mô Phỏng Tiếng Vọng nữa :( UGH!!</t>
+          <t>Chẳng có thú dữ nào cả, chỉ toàn mấy kẻ Lưu Đày phá ngày của tao. Mất thêm mấy kiện hàng nữa. Hỏng cả thiết bị đầu cuối. Giờ chẳng chạy được Mô Phỏng Tiếng Vọng nữa :( UGH!!</t>
         </is>
       </c>
     </row>
@@ -10779,7 +10779,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Cậu có thể tin tụi ta.</t>
+          <t>Cậu có thể tin tụi tao.</t>
         </is>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Ta không nói với ai cả, vì sợ anh ta gặp rắc rối nếu báo cảnh sát.</t>
+          <t>Tao không nói với ai cả, vì sợ anh tao gặp rắc rối nếu báo cảnh sát.</t>
         </is>
       </c>
     </row>
@@ -11949,7 +11949,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Nhưng ngoài kia nguy hiểm lắm với mấy vụ Tổ Tacet bùng phát ngày càng nhiều. Ta không đảm bảo được an toàn cho ngươi nếu gặp phải Tổ Tacet đang lan rộng đâu.</t>
+          <t>Nhưng ngoài kia nguy hiểm lắm với mấy vụ Tổ Tacet bùng phát ngày càng nhiều. Tao không đảm bảo được an toàn cho mày nếu gặp phải Tổ Tacet đang lan rộng đâu.</t>
         </is>
       </c>
     </row>
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>{Male=Anh ấy;Female=Cô ấy} là một Cộng Hưởng Giả mạnh mẽ. Có {Male=anh ấy;Female=cô ấy} bên cạnh, hành trình của chúng ta sẽ an toàn hơn.</t>
+          <t>{Male=him;Female=her} là một Resonator mạnh mẽ. Có {Male=him;Female=her} bên cạnh, hành trình của chúng ta sẽ an toàn hơn.</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12859,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Người giao hàng cho ta lúc nào cũng là thằng đó, ta còn biết nó làm ở đâu nữa cơ.</t>
+          <t>Người giao hàng cho tao lúc nào cũng là thằng đó, tao còn biết nó làm ở đâu nữa cơ.</t>
         </is>
       </c>
     </row>
@@ -14419,7 +14419,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Từ nhỏ ta đã xem múa lân của bọn họ rồi.</t>
+          <t>Từ nhỏ tao đã xem múa lân của bọn họ rồi.</t>
         </is>
       </c>
     </row>
@@ -15459,7 +15459,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Ừ, yên tâm đi. Ta đang canh chừng đây.</t>
+          <t>Ừ, yên tâm đi. Tao đang canh chừng đây.</t>
         </is>
       </c>
     </row>
@@ -15654,7 +15654,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Chào Rover, cậu về rồi à? Buổi biểu diễn thế nào?</t>
+          <t>Chào Vận Mệnh Giả, cậu về rồi à? Buổi biểu diễn thế nào?</t>
         </is>
       </c>
     </row>
@@ -15784,7 +15784,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Hehe, tất nhiên! Múa lân ở Kim Châu thực sự rất hoành tráng! Lần tới nhất định tớ sẽ tự mình đi xem!</t>
+          <t>Hehe, tất nhiên! Múa lân ở Jinzhou thực sự rất hoành tráng! Lần tới nhất định tớ sẽ tự mình đi xem!</t>
         </is>
       </c>
     </row>
@@ -17799,7 +17799,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>Nhưng chắc chắn tụi mình sẽ đến xem múa lân của cậu! Ta dám chắc luôn!</t>
+          <t>Nhưng chắc chắn tụi mình sẽ đến xem múa lân của cậu! Tao dám chắc luôn!</t>
         </is>
       </c>
     </row>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>May mà chúng ta bắt được Rover đó. Dù {Male=hắn;Female=cô ta} có hữu dụng cho nghiên cứu hay không, bắt {Male=hắn;Female=cô ta} làm con tin cũng sẽ giúp ta câu giờ được.</t>
+          <t>May mà chúng ta bắt được Vận Mệnh Giả đó. Dù {Male=him;Female=her} có hữu dụng cho nghiên cứu hay không, bắt {Male=him;Female=her} làm con tin cũng sẽ giúp ta câu giờ được.</t>
         </is>
       </c>
     </row>
@@ -19424,7 +19424,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Đây là tọa độ. Đưa {Male=hắn;Female=cô ta} vào phòng trong cho ta.</t>
+          <t>Đây là tọa độ. Đưa {Male=him;Female=her} vào phòng trong cho ta.</t>
         </is>
       </c>
     </row>
@@ -19554,7 +19554,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Ta đã gài theo dõi lên {Male=hắn;Female=cô ta}. {Male=Hắn;Female:Cô ta} sẽ không đi đâu được trong lãnh thổ của ta đâu.</t>
+          <t>Ta đã gài theo dõi lên {Male=He;Female=She}. {Male=He;Female=She} sẽ không đi đâu được trong lãnh thổ của ta đâu.</t>
         </is>
       </c>
     </row>
@@ -19879,7 +19879,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Đưa đây cho ta. Đừng có giở trò lừa gạt.</t>
+          <t>Đưa đây cho tao. Đừng có giở trò lừa gạt.</t>
         </is>
       </c>
     </row>
@@ -20074,7 +20074,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Chào {Male=cậu;Female=cô} bé.</t>
+          <t>Chào {Male=boy;Female=girl} bé.</t>
         </is>
       </c>
     </row>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Ít nhất cũng nói ta biết hắn định làm gì với ta chứ.</t>
+          <t>Ít nhất cũng nói tao biết hắn định làm gì với tao chứ.</t>
         </is>
       </c>
     </row>
@@ -21439,7 +21439,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Ờ... Gia đình... Gia đình của ta...</t>
+          <t>Ờ... Gia đình... Gia đình của tao...</t>
         </is>
       </c>
     </row>
@@ -21829,7 +21829,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Chưa. Nhưng mấy kẻ Lưu Đày đó đang Overclocking, ta phải hạ gục chúng.</t>
+          <t>Chưa. Nhưng mấy kẻ Lưu Đày đó đang Overclocking, tao phải hạ gục chúng.</t>
         </is>
       </c>
     </row>
@@ -22349,7 +22349,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Dừng lại đi, Dollmaker... Bố mẹ ta sẽ không đồng ý được hồi sinh thành những con rối đâu.</t>
+          <t>Dừng lại đi, Dollmaker... Bố mẹ tao sẽ không đồng ý được hồi sinh thành những con rối đâu.</t>
         </is>
       </c>
     </row>
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>Yinlin... Ít nhất ta cứ nghĩ ngươi sẽ hiểu ta chứ.</t>
+          <t>Yinlin... Ít nhất tao cứ nghĩ mày sẽ hiểu tao chứ.</t>
         </is>
       </c>
     </row>
@@ -22544,7 +22544,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Và đó cũng là lý do tại sao ta không thể hồi sinh họ từ ký ức của cậu. Từ ký ức của chính ta cũng vậy.</t>
+          <t>Và đó cũng là lý do tại sao tao không thể hồi sinh họ từ ký ức của cậu. Từ ký ức của chính tao cũng vậy.</t>
         </is>
       </c>
     </row>
@@ -22869,7 +22869,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Ta sẽ làm bất cứ điều gì để đưa họ trở lại, bất kể cái giá phải trả...</t>
+          <t>Tao sẽ làm bất cứ điều gì để đưa họ trở lại, bất kể cái giá phải trả...</t>
         </is>
       </c>
     </row>
@@ -23064,7 +23064,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Sắp đến giờ rồi. Nhà máy này đành phải bỏ lại, nhưng có mấy mẫu thử nghiệm ta phải mang theo.</t>
+          <t>Sắp đến giờ rồi. Nhà máy này đành phải bỏ lại, nhưng có mấy mẫu thử nghiệm tao phải mang theo.</t>
         </is>
       </c>
     </row>
@@ -23389,7 +23389,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Vẫn như trước thôi, Yinlin. Chỉ cần hạ gục {Male=hắn;Female=cô ta} là xong.</t>
+          <t>Vẫn như trước thôi, Yinlin. Chỉ cần hạ gục {Male=him;Female=her} là xong.</t>
         </is>
       </c>
     </row>
@@ -23454,7 +23454,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Mình sẽ để lại hai con rối ở đây. Để giả vờ chúng ta vẫn đang giam {Male=hắn;Female:cô ta} sau cánh cửa đóng kín.</t>
+          <t>Mình sẽ để lại hai con rối ở đây. Để giả vờ chúng ta vẫn đang giam {Male=him;Female=her} sau cánh cửa đóng kín.</t>
         </is>
       </c>
     </row>
@@ -25209,7 +25209,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>Lúc còn nhỏ, ta đã từng than vãn về số phận bất hạnh của mình, nhưng ta biết rõ không được làm hại người khác để bù đắp cho nó.</t>
+          <t>Lúc còn nhỏ, tao đã từng than vãn về số phận bất hạnh của mình, nhưng tao biết rõ không được làm hại người khác để bù đắp cho nó.</t>
         </is>
       </c>
     </row>
@@ -25534,7 +25534,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Ha! Đùng đụng đến công lý với ta à? Đừng có mà tưởng mình vẫn là Đội Tuần Tra nhé?</t>
+          <t>Ha! Đùng đụng đến công lý với tao à? Đừng có mà tưởng mình vẫn là Đội Tuần Tra nhé?</t>
         </is>
       </c>
     </row>
@@ -25794,7 +25794,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Ta nên đi thôi. Phần còn lại giao cho cậu, Rover.</t>
+          <t>Ta nên đi thôi. Phần còn lại giao cho cậu, Vận Mệnh Giả.</t>
         </is>
       </c>
     </row>
@@ -25924,7 +25924,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Lần sau gặp lại, ta sẽ giải thích tất cả, và cảm ơn cậu cho đàng hoàng.</t>
+          <t>Lần sau gặp lại, tao sẽ giải thích tất cả, và cảm ơn cậu cho đàng hoàng.</t>
         </is>
       </c>
     </row>
@@ -26249,7 +26249,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Ta không sao. Còn những người khác thì sao?</t>
+          <t>Tao không sao. Còn những người khác thì sao?</t>
         </is>
       </c>
     </row>
@@ -27939,7 +27939,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Tất cả các con rối đều được cung cấp năng lượng từ những bình kim loại này... Đó là lý do người không phải Cộng Hưởng Giả vẫn có thể kích hoạt chúng.</t>
+          <t>Tất cả các con rối đều được cung cấp năng lượng từ những bình kim loại này... Đó là lý do người không phải Resonator vẫn có thể kích hoạt chúng.</t>
         </is>
       </c>
     </row>
@@ -28329,7 +28329,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Đừng... lại gần ta...</t>
+          <t>Đừng... lại gần tao...</t>
         </is>
       </c>
     </row>
@@ -29369,7 +29369,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Tacet Discord... Chúng sẽ không... Không... Ta sẽ... Ta không thể... Giúp ta...</t>
+          <t>Tacet Discord... Chúng sẽ không... Không... Tao sẽ... Tao không thể... Giúp tao...</t>
         </is>
       </c>
     </row>
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Tại sao lại không? Hãy tận hưởng tuổi trẻ của cậu đi! Nếu ta còn trẻ, ta đã đăng ký ngay rồi.</t>
+          <t>Tại sao lại không? Hãy tận hưởng tuổi trẻ của cậu đi! Nếu tao còn trẻ, tao đã đăng ký ngay rồi.</t>
         </is>
       </c>
     </row>
@@ -30279,7 +30279,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Tất nhiên rồi! Đại hội Thể thao Bờ Sông Kim Châu là sự kiện để tất cả mọi người cùng vui vẻ.</t>
+          <t>Tất nhiên rồi! Đại hội Thể thao Bờ Sông Jinzhou là sự kiện để tất cả mọi người cùng vui vẻ.</t>
         </is>
       </c>
     </row>
@@ -30409,7 +30409,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Chỉ một số sự kiện đặc biệt yêu cầu người tham gia phải là Cộng Hưởng Giả. Ngoài ra, không có hạn chế đặc biệt nào cho bất kỳ sự kiện nào khác.</t>
+          <t>Chỉ một số sự kiện đặc biệt yêu cầu người tham gia phải là Resonator. Ngoài ra, không có hạn chế đặc biệt nào cho bất kỳ sự kiện nào khác.</t>
         </is>
       </c>
     </row>
@@ -32164,7 +32164,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>{PlayerName} cũng là một Cộng Hưởng Giả. {Male=Hắn;Female:Cô ấy} hoàn toàn đủ điều kiện tham gia cuộc đua Gulpuff Relay.</t>
+          <t>{PlayerName} cũng là một Resonator. {Male=He's;Female=She's} hoàn toàn đủ điều kiện tham gia cuộc đua Gulpuff Relay.</t>
         </is>
       </c>
     </row>
